--- a/词语表模板.xlsx
+++ b/词语表模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FHSS\Teaching 2026\Department\AI 词语\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767755EA-26EA-4F3D-8960-6F4E96617AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDCDCE4-CA06-4342-83B4-4E7AD2647EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="7130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2620" yWindow="2620" windowWidth="14400" windowHeight="7130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="词语表" sheetId="1" r:id="rId1"/>
@@ -1520,25 +1520,25 @@
     <t>阐述</t>
   </si>
   <si>
-    <t>论说，说明 elaborate</t>
+    <t>论说，说明</t>
   </si>
   <si>
     <t>铿锵</t>
   </si>
   <si>
-    <t>声音大，清晰，而有节奏 sonorous</t>
+    <t>声音大，清晰，而有节奏</t>
   </si>
   <si>
     <t>雅俗</t>
   </si>
   <si>
-    <t>雅人和俗人 refined and vulgar</t>
+    <t>雅人和俗人</t>
   </si>
   <si>
     <t>僵硬</t>
   </si>
   <si>
-    <t>很少动，不灵活 stiff</t>
+    <t>很少动，不灵活</t>
   </si>
   <si>
     <t>言简意赅</t>
@@ -1550,7 +1550,7 @@
     <t>啰嗦</t>
   </si>
   <si>
-    <t>话说的又长又多，言语反复 long-winded</t>
+    <t>话说的又长又多，言语反复</t>
   </si>
   <si>
     <t>遐想</t>
@@ -1562,25 +1562,25 @@
     <t>枯燥</t>
   </si>
   <si>
-    <t>单调，无趣味 boring</t>
+    <t>单调，无趣味</t>
   </si>
   <si>
     <t>筛选</t>
   </si>
   <si>
-    <t>用淘汰法来挑选适合需要的 select</t>
+    <t>用淘汰法来挑选适合需要的</t>
   </si>
   <si>
     <t>勿</t>
   </si>
   <si>
-    <t>禁止，劝阻 do not</t>
+    <t>禁止，劝阻</t>
   </si>
   <si>
     <t>浏览</t>
   </si>
   <si>
-    <t>大略地看，泛泛地阅读 browse</t>
+    <t>大略地看，泛泛地阅读</t>
   </si>
   <si>
     <t>孤岛</t>
@@ -1598,19 +1598,19 @@
     <t>体恤</t>
   </si>
   <si>
-    <t>替他人实际处境着想而怜悯。sympathise</t>
+    <t>替他人实际处境着想而怜悯</t>
   </si>
   <si>
     <t>关键</t>
   </si>
   <si>
-    <t>对事物最重要的部分，起决定性作用。key</t>
+    <t>对事物最重要的部分，起决定性作用</t>
   </si>
   <si>
     <t>哲学</t>
   </si>
   <si>
-    <t>研究自然、社会和思维的最一般规律的科学（philosophy）</t>
+    <t>研究自然、社会和思维的最一般规律的科学</t>
   </si>
   <si>
     <t>颇</t>
@@ -1622,7 +1622,7 @@
     <t>谦逊</t>
   </si>
   <si>
-    <t>不自大，不虚夸，谦虚 （humble)</t>
+    <t>不自大，不虚夸，谦虚</t>
   </si>
   <si>
     <t>畅所欲言</t>
@@ -1682,7 +1682,7 @@
     <t>崛起</t>
   </si>
   <si>
-    <t>出现兴盛起来；兴起 （英文：prominence)</t>
+    <t>出现兴盛起来；兴起</t>
   </si>
   <si>
     <t>颠覆</t>
@@ -1700,7 +1700,7 @@
     <t>小卒</t>
   </si>
   <si>
-    <t>小兵；无名的人（英文：private）</t>
+    <t>小兵；无名的人</t>
   </si>
   <si>
     <t>迄今</t>
@@ -1718,7 +1718,7 @@
     <t>屏幕</t>
   </si>
   <si>
-    <t>显示屏 （英文：screen）</t>
+    <t>显示屏</t>
   </si>
   <si>
     <t>按钮</t>
@@ -1730,7 +1730,7 @@
     <t>疆界</t>
   </si>
   <si>
-    <t>国家或地域的边界 （英文：boundary)</t>
+    <t>国家或地域的边界</t>
   </si>
   <si>
     <t>毋庸</t>
@@ -1778,7 +1778,7 @@
     <t>肤色</t>
   </si>
   <si>
-    <t>皮肤的颜色 (skin colour)</t>
+    <t>皮肤的颜色</t>
   </si>
   <si>
     <t>剑拔弩张</t>
@@ -1814,7 +1814,7 @@
     <t>刺猬</t>
   </si>
   <si>
-    <t>身上长着短而密的硬刺的动物 （hedgehog）</t>
+    <t>身上长着短而密的硬刺的动物</t>
   </si>
   <si>
     <t>报酬</t>
